--- a/excel/LoginData.xlsx
+++ b/excel/LoginData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29505"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29509"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro 5\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro 5\OneDrive\Universidad\TestPage\TestPage-Calidad\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C7E7018-5BF9-4D5D-8FAC-47C7A361A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA02883-C868-4C9E-8E0A-2D1F2622B992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E79BDA6-CB64-4C30-B948-6B7CCE5D8053}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Email</t>
   </si>
@@ -47,12 +47,6 @@
     <t>ResultadoEsperado</t>
   </si>
   <si>
-    <t>demo@demo.com</t>
-  </si>
-  <si>
-    <t>demo</t>
-  </si>
-  <si>
     <t>Exito</t>
   </si>
   <si>
@@ -60,13 +54,16 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>pepe1213@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +75,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -115,10 +120,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,8 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -478,29 +488,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>123456789</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>1234</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{441DEAF5-E684-4CBC-82F1-8EEEB929FB83}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>